--- a/Documentation/Week 8/TimeSheet_Group21_Wk8.xlsx
+++ b/Documentation/Week 8/TimeSheet_Group21_Wk8.xlsx
@@ -2060,8 +2060,12 @@
         <v>35</v>
       </c>
       <c r="O14" s="19" t="n"/>
-      <c r="P14" s="18" t="n"/>
-      <c r="Q14" s="19" t="n"/>
+      <c r="P14" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q14" s="19" t="n">
+        <v>4.5</v>
+      </c>
       <c r="R14" s="18" t="n"/>
       <c r="S14" s="19" t="n"/>
       <c r="T14" s="18" t="n"/>
@@ -2168,7 +2172,9 @@
         <v>40</v>
       </c>
       <c r="O17" s="19" t="n"/>
-      <c r="P17" s="18" t="n"/>
+      <c r="P17" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="Q17" s="19" t="n"/>
       <c r="R17" s="18" t="n"/>
       <c r="S17" s="19" t="n"/>
@@ -2208,7 +2214,9 @@
         <v>5</v>
       </c>
       <c r="O18" s="19" t="n"/>
-      <c r="P18" s="18" t="n"/>
+      <c r="P18" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="Q18" s="19" t="n"/>
       <c r="R18" s="18" t="n"/>
       <c r="S18" s="19" t="n"/>
@@ -2268,8 +2276,12 @@
       <c r="O19" s="19" t="n">
         <v>1.25</v>
       </c>
-      <c r="P19" s="18" t="n"/>
-      <c r="Q19" s="19" t="n"/>
+      <c r="P19" s="18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Q19" s="19" t="n">
+        <v>5.25</v>
+      </c>
       <c r="R19" s="18" t="n"/>
       <c r="S19" s="19" t="n"/>
       <c r="T19" s="18" t="n"/>
@@ -2328,8 +2340,12 @@
       <c r="O20" s="19" t="n">
         <v>5.25</v>
       </c>
-      <c r="P20" s="18" t="n"/>
-      <c r="Q20" s="19" t="n"/>
+      <c r="P20" s="18" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q20" s="19" t="n">
+        <v>5.5</v>
+      </c>
       <c r="R20" s="18" t="n"/>
       <c r="S20" s="19" t="n"/>
       <c r="T20" s="18" t="n"/>
@@ -2420,8 +2436,12 @@
       <c r="O22" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="P22" s="18" t="n"/>
-      <c r="Q22" s="19" t="n"/>
+      <c r="P22" s="18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Q22" s="19" t="n">
+        <v>4.5</v>
+      </c>
       <c r="R22" s="18" t="n"/>
       <c r="S22" s="19" t="n"/>
       <c r="T22" s="18" t="n"/>
@@ -2514,7 +2534,9 @@
         <v>3</v>
       </c>
       <c r="O24" s="19" t="n"/>
-      <c r="P24" s="18" t="n"/>
+      <c r="P24" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="Q24" s="19" t="n"/>
       <c r="R24" s="18" t="n"/>
       <c r="S24" s="19" t="n"/>
@@ -2554,8 +2576,12 @@
       <c r="O25" s="19" t="n">
         <v>16.83</v>
       </c>
-      <c r="P25" s="18" t="n"/>
-      <c r="Q25" s="19" t="n"/>
+      <c r="P25" s="18" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q25" s="19" t="n">
+        <v>6</v>
+      </c>
       <c r="R25" s="18" t="n"/>
       <c r="S25" s="19" t="n"/>
       <c r="T25" s="18" t="n"/>
@@ -3424,10 +3450,18 @@
       <c r="AB17" s="17" t="n">
         <v>4.5</v>
       </c>
-      <c r="AC17" s="20" t="n"/>
-      <c r="AD17" s="17" t="n"/>
-      <c r="AE17" s="20" t="n"/>
-      <c r="AF17" s="17" t="n"/>
+      <c r="AC17" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD17" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE17" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF17" s="17" t="n">
+        <v>3.33</v>
+      </c>
       <c r="AG17" s="20" t="n"/>
       <c r="AH17" s="17" t="n"/>
       <c r="AI17" s="20" t="n"/>
@@ -3521,10 +3555,18 @@
       <c r="AB18" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="AC18" s="20" t="n"/>
-      <c r="AD18" s="17" t="n"/>
-      <c r="AE18" s="20" t="n"/>
-      <c r="AF18" s="17" t="n"/>
+      <c r="AC18" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD18" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE18" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF18" s="17" t="n">
+        <v>0.75</v>
+      </c>
       <c r="AG18" s="20" t="n"/>
       <c r="AH18" s="17" t="n"/>
       <c r="AI18" s="20" t="n"/>
@@ -6395,7 +6437,9 @@
       <c r="G9" s="20" t="n">
         <v>8.5</v>
       </c>
-      <c r="H9" s="17" t="n"/>
+      <c r="H9" s="17" t="n">
+        <v>4.25</v>
+      </c>
       <c r="I9" s="20" t="n"/>
       <c r="J9" s="17" t="n"/>
       <c r="K9" s="20" t="n"/>
@@ -6428,7 +6472,9 @@
       <c r="G10" s="20" t="n">
         <v>10.83</v>
       </c>
-      <c r="H10" s="17" t="n"/>
+      <c r="H10" s="17" t="n">
+        <v>2.17</v>
+      </c>
       <c r="I10" s="20" t="n"/>
       <c r="J10" s="17" t="n"/>
       <c r="K10" s="20" t="n"/>
@@ -6461,7 +6507,9 @@
       <c r="G11" s="20" t="n">
         <v>3.25</v>
       </c>
-      <c r="H11" s="17" t="n"/>
+      <c r="H11" s="17" t="n">
+        <v>3.25</v>
+      </c>
       <c r="I11" s="20" t="n"/>
       <c r="J11" s="17" t="n"/>
       <c r="K11" s="20" t="n"/>
@@ -6494,7 +6542,9 @@
       <c r="G12" s="20" t="n">
         <v>2.5</v>
       </c>
-      <c r="H12" s="17" t="n"/>
+      <c r="H12" s="17" t="n">
+        <v>3.75</v>
+      </c>
       <c r="I12" s="20" t="n"/>
       <c r="J12" s="17" t="n"/>
       <c r="K12" s="20" t="n"/>
@@ -6527,7 +6577,9 @@
       <c r="G13" s="20" t="n">
         <v>6.5</v>
       </c>
-      <c r="H13" s="17" t="n"/>
+      <c r="H13" s="17" t="n">
+        <v>4.58</v>
+      </c>
       <c r="I13" s="20" t="n"/>
       <c r="J13" s="17" t="n"/>
       <c r="K13" s="20" t="n"/>
@@ -6560,7 +6612,9 @@
       <c r="G14" s="20" t="n">
         <v>5.75</v>
       </c>
-      <c r="H14" s="17" t="n"/>
+      <c r="H14" s="17" t="n">
+        <v>14.33</v>
+      </c>
       <c r="I14" s="20" t="n"/>
       <c r="J14" s="17" t="n"/>
       <c r="K14" s="20" t="n"/>
